--- a/files/九龙-九龙塘-喇沙汇.xlsx
+++ b/files/九龙-九龙塘-喇沙汇.xlsx
@@ -200,61 +200,61 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -640,6 +640,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -697,6 +701,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -743,6 +767,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -789,6 +833,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -835,6 +899,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -881,13 +965,33 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
